--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_LITHIUM IBERIA SAGRADO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_LITHIUM IBERIA SAGRADO.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1393</v>
+        <v>4.3654</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6389</v>
+        <v>5.1405</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4997</v>
+        <v>-0.7751</v>
       </c>
       <c r="G2" t="n">
-        <v>4.1232</v>
+        <v>4.2236</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1756</v>
+        <v>0.174</v>
       </c>
       <c r="I2" t="n">
-        <v>3.9476</v>
+        <v>4.0497</v>
       </c>
       <c r="J2" t="n">
-        <v>6.5319</v>
+        <v>6.8274</v>
       </c>
       <c r="K2" t="n">
-        <v>2.4829</v>
+        <v>2.6121</v>
       </c>
       <c r="L2" t="n">
-        <v>4.0489</v>
+        <v>4.2154</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.4086</v>
+        <v>-2.6038</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.3073</v>
+        <v>-2.4381</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1013</v>
+        <v>-0.1657</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.0011</v>
+        <v>-3.8947</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4708</v>
+        <v>-0.4544</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.211</v>
+        <v>-0.1827</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2598</v>
+        <v>-0.2717</v>
       </c>
       <c r="V2" t="n">
-        <v>2.4874</v>
+        <v>2.5436</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3192</v>
+        <v>2.3905</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1682</v>
+        <v>0.1531</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1621</v>
+        <v>1.1251</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2743</v>
+        <v>2.4106</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1122</v>
+        <v>-1.2855</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6761</v>
+        <v>1.6369</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3876</v>
+        <v>0.3222</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2886</v>
+        <v>1.3147</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9635</v>
+        <v>2.0368</v>
       </c>
       <c r="K3" t="n">
-        <v>0.16</v>
+        <v>0.1642</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8036</v>
+        <v>1.8726</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2874</v>
+        <v>-0.3999</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2276</v>
+        <v>0.158</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.515</v>
+        <v>-0.5578</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5422</v>
+        <v>-0.5286</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1113</v>
+        <v>0.1265</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6534</v>
+        <v>-0.655</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1719</v>
+        <v>-0.178</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.3717</v>
+        <v>-1.3991</v>
       </c>
     </row>
     <row r="4">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2855</v>
+        <v>0.2711</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0245</v>
+        <v>-0.0213</v>
       </c>
       <c r="F4" t="n">
-        <v>0.31</v>
+        <v>0.2924</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1113</v>
+        <v>0.1011</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1999</v>
+        <v>-0.2053</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3112</v>
+        <v>0.3063</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0713</v>
+        <v>0.0605</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1999</v>
+        <v>-0.2053</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2712</v>
+        <v>0.2658</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0258</v>
+        <v>-0.0247</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0645</v>
+        <v>-0.0618</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0387</v>
+        <v>0.0371</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2855</v>
+        <v>0.2711</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0245</v>
+        <v>-0.0213</v>
       </c>
       <c r="F5" t="n">
-        <v>0.31</v>
+        <v>0.2924</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1113</v>
+        <v>0.1011</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1999</v>
+        <v>-0.2053</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3112</v>
+        <v>0.3063</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0713</v>
+        <v>0.0605</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1999</v>
+        <v>-0.2053</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2712</v>
+        <v>0.2658</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0258</v>
+        <v>-0.0247</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0645</v>
+        <v>-0.0618</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0387</v>
+        <v>0.0371</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2012</v>
+        <v>-0.0114</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5461</v>
+        <v>0.6288</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.345</v>
+        <v>-0.6402</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5253</v>
+        <v>-0.627</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.3614</v>
+        <v>-1.4292</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8361</v>
+        <v>0.8022</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3617</v>
+        <v>0.3992</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0818</v>
+        <v>0.1155</v>
       </c>
       <c r="L6" t="n">
-        <v>0.28</v>
+        <v>0.2837</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8871</v>
+        <v>-1.0262</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4432</v>
+        <v>-1.5447</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5561</v>
+        <v>0.5185</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S6" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0742</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.0498</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1528</v>
+        <v>0.124</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9513</v>
+        <v>-1.0164</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2111</v>
+        <v>-1.2959</v>
       </c>
     </row>
     <row r="7">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4433</v>
+        <v>-0.4631</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1534</v>
+        <v>-0.145</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2899</v>
+        <v>-0.3182</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.353</v>
+        <v>-0.3766</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3999</v>
+        <v>-0.4105</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0469</v>
+        <v>0.034</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.393</v>
+        <v>-0.4171</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3999</v>
+        <v>-0.4105</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0069</v>
+        <v>-0.0066</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2903</v>
+        <v>-0.2813</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1934</v>
+        <v>-0.1855</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0969</v>
+        <v>-0.0958</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8875</v>
+        <v>-0.8522999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8373</v>
+        <v>2.1149</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.7249</v>
+        <v>-2.9672</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4153</v>
+        <v>0.444</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9946</v>
+        <v>1.0715</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5793</v>
+        <v>-0.6276</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1666</v>
+        <v>2.3478</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9667</v>
+        <v>2.1451</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2</v>
+        <v>0.2026</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7514</v>
+        <v>-1.9038</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9721</v>
+        <v>-1.0736</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7793</v>
+        <v>-0.8302</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.8005</v>
+        <v>-1.7526</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S8" t="n">
-        <v>1.9497</v>
+        <v>1.907</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1519</v>
+        <v>2.1292</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2022</v>
+        <v>-0.2222</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.452</v>
+        <v>-1.4506</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5196</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.9716</v>
+        <v>-2.0096</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5234</v>
+        <v>-2.495</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6759</v>
+        <v>-1.4453</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8475</v>
+        <v>-1.0497</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2804</v>
+        <v>-1.2545</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7693</v>
+        <v>-0.7456</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5112</v>
+        <v>-0.509</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5491</v>
+        <v>0.7033</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5453</v>
+        <v>0.6544</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0038</v>
+        <v>0.0489</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8295</v>
+        <v>-1.9578</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3145</v>
+        <v>-1.4</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.515</v>
+        <v>-0.5578</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7231</v>
+        <v>-0.7078</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2244</v>
+        <v>-0.2012</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4987</v>
+        <v>-0.5066000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0803</v>
+        <v>0.0516</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0803</v>
+        <v>0.0516</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9601</v>
+        <v>-4.0483</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5386</v>
+        <v>-1.4558</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.4215</v>
+        <v>-2.5925</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8659</v>
+        <v>-1.9268</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8154</v>
+        <v>-0.8308</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0505</v>
+        <v>-1.096</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0418</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0418</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9077</v>
+        <v>-2.0013</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8572</v>
+        <v>-0.9052</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0505</v>
+        <v>-1.096</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5746</v>
+        <v>-0.5625</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.5565</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0055</v>
+        <v>-0.006</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1195</v>
+        <v>-1.1695</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1195</v>
+        <v>-1.1695</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.165</v>
+        <v>-7.186</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5935</v>
+        <v>-2.3581</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.5715</v>
+        <v>-4.8279</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.2039</v>
+        <v>-1.2555</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.6953</v>
+        <v>-3.7306</v>
       </c>
       <c r="I11" t="n">
-        <v>2.4915</v>
+        <v>2.4751</v>
       </c>
       <c r="J11" t="n">
-        <v>1.6253</v>
+        <v>1.7286</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9743000000000001</v>
+        <v>-0.9056</v>
       </c>
       <c r="L11" t="n">
-        <v>2.5996</v>
+        <v>2.6342</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.8292</v>
+        <v>-2.9841</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.721</v>
+        <v>-2.825</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1082</v>
+        <v>-0.1591</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.6007</v>
+        <v>-2.5316</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.0011</v>
+        <v>-3.8947</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.361</v>
+        <v>-0.3463</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2177</v>
+        <v>-0.192</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1432</v>
+        <v>-0.1543</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.9994</v>
+        <v>-3.0526</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.9994</v>
+        <v>-3.0526</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.8607</v>
+        <v>-7.8694</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.5661</v>
+        <v>-4.406</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.2946</v>
+        <v>-3.4634</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.906</v>
+        <v>-3.9745</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.5814</v>
+        <v>-1.655</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.3246</v>
+        <v>-2.3195</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.8121</v>
+        <v>-1.7443</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.538</v>
+        <v>-0.5208</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2741</v>
+        <v>-1.2235</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.0938</v>
+        <v>-2.2302</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.0433</v>
+        <v>-1.1342</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.0505</v>
+        <v>-1.096</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.9547</v>
+        <v>-1.8949</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7534</v>
+        <v>-0.7143</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.2013</v>
+        <v>-1.1806</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.966900000000001</v>
+        <v>-9.8612</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.8605</v>
+        <v>-7.4822</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1064</v>
+        <v>-2.3791</v>
       </c>
       <c r="G13" t="n">
-        <v>-8.0465</v>
+        <v>-7.9275</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.6009</v>
+        <v>-4.5531</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.4456</v>
+        <v>-3.3744</v>
       </c>
       <c r="J13" t="n">
-        <v>-6.7089</v>
+        <v>-6.4105</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.3646</v>
+        <v>-3.2018</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.3443</v>
+        <v>-3.2087</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.3377</v>
+        <v>-1.5169</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.2363</v>
+        <v>-1.3512</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1013</v>
+        <v>-0.1657</v>
       </c>
       <c r="P13" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3488</v>
+        <v>-1.3137</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4111</v>
+        <v>-0.3775</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9378</v>
+        <v>-0.9362</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.3717</v>
+        <v>-1.3991</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.6315</v>
+        <v>-1.6785</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-26.7333</v>
+        <v>-26.754</v>
       </c>
       <c r="E14" t="n">
-        <v>-9.1404</v>
+        <v>-7.0402</v>
       </c>
       <c r="F14" t="n">
-        <v>-17.5932</v>
+        <v>-19.714</v>
       </c>
       <c r="G14" t="n">
-        <v>-10.7438</v>
+        <v>-10.8357</v>
       </c>
       <c r="H14" t="n">
-        <v>-12.0656</v>
+        <v>-12.1977</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3219</v>
+        <v>1.3618</v>
       </c>
       <c r="J14" t="n">
-        <v>4.838899999999999</v>
+        <v>6.084200000000002</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4015999999999997</v>
+        <v>1.1375</v>
       </c>
       <c r="L14" t="n">
-        <v>4.437500000000002</v>
+        <v>4.946700000000002</v>
       </c>
       <c r="M14" t="n">
-        <v>-15.5828</v>
+        <v>-16.9201</v>
       </c>
       <c r="N14" t="n">
-        <v>-12.467</v>
+        <v>-13.3351</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.1157</v>
+        <v>-3.5848</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.0012</v>
+        <v>-4.868600000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-18.0052</v>
+        <v>-17.5263</v>
       </c>
       <c r="R14" t="n">
-        <v>13.0038</v>
+        <v>12.6578</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.2901</v>
+        <v>-4.1577</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5322999999999998</v>
+        <v>-0.3274000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.7576</v>
+        <v>-3.8302</v>
       </c>
       <c r="V14" t="n">
-        <v>-6.6979</v>
+        <v>-6.892099999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>4.5582</v>
+        <v>4.7296</v>
       </c>
       <c r="X14" t="n">
-        <v>-11.2561</v>
+        <v>-11.6216</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_LITHIUM IBERIA SAGRADO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_LITHIUM IBERIA SAGRADO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3654</v>
+        <v>4.5656</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1405</v>
+        <v>5.0408</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7751</v>
+        <v>-0.4753</v>
       </c>
       <c r="G2" t="n">
         <v>4.2236</v>
@@ -610,13 +610,13 @@
         <v>1.9474</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4544</v>
+        <v>-0.2543</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1827</v>
+        <v>-0.2824</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2717</v>
+        <v>0.0281</v>
       </c>
       <c r="V2" t="n">
         <v>2.5436</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1251</v>
+        <v>1.6405</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4106</v>
+        <v>2.7096</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.2855</v>
+        <v>-1.0691</v>
       </c>
       <c r="G3" t="n">
         <v>1.6369</v>
@@ -688,13 +688,13 @@
         <v>1.1684</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5286</v>
+        <v>-0.0132</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1265</v>
+        <v>0.4255</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.655</v>
+        <v>-0.4386</v>
       </c>
       <c r="V3" t="n">
         <v>-0.178</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2711</v>
+        <v>0.4264</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0213</v>
+        <v>0.0784</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2924</v>
+        <v>0.348</v>
       </c>
       <c r="G4" t="n">
         <v>0.1011</v>
@@ -766,13 +766,13 @@
         <v>0.1947</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0247</v>
+        <v>0.1306</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0618</v>
+        <v>0.0378</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0371</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2711</v>
+        <v>0.4264</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0213</v>
+        <v>0.0784</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2924</v>
+        <v>0.348</v>
       </c>
       <c r="G5" t="n">
         <v>0.1011</v>
@@ -844,13 +844,13 @@
         <v>0.1947</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0247</v>
+        <v>0.1306</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0618</v>
+        <v>0.0378</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0371</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0114</v>
+        <v>-0.0786</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6288</v>
+        <v>0.7285</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6402</v>
+        <v>-0.8071</v>
       </c>
       <c r="G6" t="n">
         <v>-0.627</v>
@@ -922,13 +922,13 @@
         <v>1.5579</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0742</v>
+        <v>0.0069</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0498</v>
+        <v>0.0499</v>
       </c>
       <c r="U6" t="n">
-        <v>0.124</v>
+        <v>-0.0429</v>
       </c>
       <c r="V6" t="n">
         <v>-1.0164</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4631</v>
+        <v>-0.3078</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.145</v>
+        <v>-0.0453</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3182</v>
+        <v>-0.2625</v>
       </c>
       <c r="G7" t="n">
         <v>-0.3766</v>
@@ -1000,13 +1000,13 @@
         <v>0.1947</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2813</v>
+        <v>-0.126</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1855</v>
+        <v>-0.0858</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0958</v>
+        <v>-0.0401</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8522999999999999</v>
+        <v>-2.077</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1149</v>
+        <v>0.8191000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.9672</v>
+        <v>-2.8961</v>
       </c>
       <c r="G8" t="n">
         <v>0.444</v>
@@ -1078,13 +1078,13 @@
         <v>1.1684</v>
       </c>
       <c r="S8" t="n">
-        <v>1.907</v>
+        <v>0.6823</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1292</v>
+        <v>0.8334</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2222</v>
+        <v>-0.1511</v>
       </c>
       <c r="V8" t="n">
         <v>-1.4506</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.495</v>
+        <v>-2.8118</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4453</v>
+        <v>-1.6446</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0497</v>
+        <v>-1.1672</v>
       </c>
       <c r="G9" t="n">
         <v>-1.2545</v>
@@ -1156,13 +1156,13 @@
         <v>1.3632</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7078</v>
+        <v>-1.0247</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2012</v>
+        <v>-0.4005</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5066000000000001</v>
+        <v>-0.6241</v>
       </c>
       <c r="V9" t="n">
         <v>0.0516</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0483</v>
+        <v>-3.8552</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4558</v>
+        <v>-1.2564</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5925</v>
+        <v>-2.5988</v>
       </c>
       <c r="G10" t="n">
         <v>-1.9268</v>
@@ -1234,13 +1234,13 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5625</v>
+        <v>-0.3694</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5565</v>
+        <v>-0.3572</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.006</v>
+        <v>-0.0122</v>
       </c>
       <c r="V10" t="n">
         <v>-1.1695</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. LEON TEJERA</t>
+          <t>S. KVERNADZE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.186</v>
+        <v>-6.783</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3581</v>
+        <v>-3.808</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.8279</v>
+        <v>-2.975</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.2555</v>
+        <v>-3.9745</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.7306</v>
+        <v>-1.655</v>
       </c>
       <c r="I11" t="n">
-        <v>2.4751</v>
+        <v>-2.3195</v>
       </c>
       <c r="J11" t="n">
-        <v>1.7286</v>
+        <v>-1.7443</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9056</v>
+        <v>-0.5208</v>
       </c>
       <c r="L11" t="n">
-        <v>2.6342</v>
+        <v>-1.2235</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.9841</v>
+        <v>-2.2302</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.825</v>
+        <v>-1.1342</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1591</v>
+        <v>-1.096</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.5316</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.8947</v>
+        <v>-1.9474</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3632</v>
+        <v>1.1684</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3463</v>
+        <v>-0.8085</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.192</v>
+        <v>-0.1163</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1543</v>
+        <v>-0.6922</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.0526</v>
+        <v>-1.2211</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.0526</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. KVERNADZE</t>
+          <t>B. LEON TEJERA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.8694</v>
+        <v>-7.4078</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.406</v>
+        <v>-2.6571</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.4634</v>
+        <v>-4.7507</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.9745</v>
+        <v>-1.2555</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.655</v>
+        <v>-3.7306</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.3195</v>
+        <v>2.4751</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.7443</v>
+        <v>1.7286</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5208</v>
+        <v>-0.9056</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2235</v>
+        <v>2.6342</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.2302</v>
+        <v>-2.9841</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1342</v>
+        <v>-2.825</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.096</v>
+        <v>-0.1591</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.7789</v>
+        <v>-2.5316</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9474</v>
+        <v>-3.8947</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1684</v>
+        <v>1.3632</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8949</v>
+        <v>-0.5681</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7143</v>
+        <v>-0.491</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.1806</v>
+        <v>-0.0771</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2211</v>
+        <v>-3.0526</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2211</v>
+        <v>-3.0526</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.8612</v>
+        <v>-9.162699999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.4822</v>
+        <v>-7.0835</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.3791</v>
+        <v>-2.0792</v>
       </c>
       <c r="G13" t="n">
         <v>-7.9275</v>
@@ -1468,13 +1468,13 @@
         <v>1.7526</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3137</v>
+        <v>-0.6151</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3775</v>
+        <v>0.0212</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9362</v>
+        <v>-0.6364</v>
       </c>
       <c r="V13" t="n">
         <v>-1.3991</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-26.754</v>
+        <v>-25.425</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.0402</v>
+        <v>-7.0401</v>
       </c>
       <c r="F14" t="n">
-        <v>-19.714</v>
+        <v>-18.385</v>
       </c>
       <c r="G14" t="n">
         <v>-10.8357</v>
@@ -1525,7 +1525,7 @@
         <v>1.1375</v>
       </c>
       <c r="L14" t="n">
-        <v>4.946700000000002</v>
+        <v>4.9467</v>
       </c>
       <c r="M14" t="n">
         <v>-16.9201</v>
@@ -1546,16 +1546,16 @@
         <v>12.6578</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.1577</v>
+        <v>-2.8289</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3274000000000001</v>
+        <v>-0.3276</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.8302</v>
+        <v>-2.501</v>
       </c>
       <c r="V14" t="n">
-        <v>-6.892099999999999</v>
+        <v>-6.8921</v>
       </c>
       <c r="W14" t="n">
         <v>4.7296</v>
